--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/163.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/163.xlsx
@@ -426,13 +426,13 @@
         <v>-1.536500697823518</v>
       </c>
       <c r="E2">
-        <v>-6.083182723743331</v>
+        <v>-6.286407051785554</v>
       </c>
       <c r="F2">
-        <v>-4.421304507780787</v>
+        <v>-3.888256811497389</v>
       </c>
       <c r="G2">
-        <v>-9.436846942727962</v>
+        <v>-10.00736980823826</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.504340326511201</v>
       </c>
       <c r="E3">
-        <v>-7.20264866928349</v>
+        <v>-6.491655607709205</v>
       </c>
       <c r="F3">
-        <v>-4.26935901113578</v>
+        <v>-4.283928313704865</v>
       </c>
       <c r="G3">
-        <v>-9.509013524938535</v>
+        <v>-10.53768609817411</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.461295409357677</v>
       </c>
       <c r="E4">
-        <v>-7.145721222533066</v>
+        <v>-8.931321166127526</v>
       </c>
       <c r="F4">
-        <v>-4.170136668121668</v>
+        <v>-3.750233673555011</v>
       </c>
       <c r="G4">
-        <v>-9.379826106359555</v>
+        <v>-9.103150573460505</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.392215187061183</v>
       </c>
       <c r="E5">
-        <v>-8.162884411765942</v>
+        <v>-6.618154000639469</v>
       </c>
       <c r="F5">
-        <v>-4.238533759197667</v>
+        <v>-3.961583187235194</v>
       </c>
       <c r="G5">
-        <v>-9.198937898093778</v>
+        <v>-9.117564688738492</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-1.266300391732065</v>
       </c>
       <c r="E6">
-        <v>-9.039130546828135</v>
+        <v>-8.865101290713362</v>
       </c>
       <c r="F6">
-        <v>-4.221781318024148</v>
+        <v>-3.739743997424097</v>
       </c>
       <c r="G6">
-        <v>-8.151093955640279</v>
+        <v>-8.892868031351538</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-1.059334495776186</v>
       </c>
       <c r="E7">
-        <v>-9.222062782841986</v>
+        <v>-9.798243173207924</v>
       </c>
       <c r="F7">
-        <v>-4.180794217079618</v>
+        <v>-3.886080007716618</v>
       </c>
       <c r="G7">
-        <v>-8.70984783175847</v>
+        <v>-9.458769375289016</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.7513012859832399</v>
       </c>
       <c r="E8">
-        <v>-9.793266380273494</v>
+        <v>-10.7495759357913</v>
       </c>
       <c r="F8">
-        <v>-3.907495670958148</v>
+        <v>-4.037566229646147</v>
       </c>
       <c r="G8">
-        <v>-8.300707440196563</v>
+        <v>-8.71920674399799</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.3329519812227416</v>
       </c>
       <c r="E9">
-        <v>-10.64324283761719</v>
+        <v>-11.54137508755845</v>
       </c>
       <c r="F9">
-        <v>-3.976942759056083</v>
+        <v>-3.759845976608771</v>
       </c>
       <c r="G9">
-        <v>-7.775737681306634</v>
+        <v>-8.494947078622221</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>0.1912089759216762</v>
       </c>
       <c r="E10">
-        <v>-11.63046828518536</v>
+        <v>-11.54025202600455</v>
       </c>
       <c r="F10">
-        <v>-3.816314594729679</v>
+        <v>-3.726512134500601</v>
       </c>
       <c r="G10">
-        <v>-8.365511369127796</v>
+        <v>-8.041465240107314</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.8004293381554478</v>
       </c>
       <c r="E11">
-        <v>-12.91038259329128</v>
+        <v>-13.03840255348813</v>
       </c>
       <c r="F11">
-        <v>-3.667093864112186</v>
+        <v>-3.516294178697</v>
       </c>
       <c r="G11">
-        <v>-7.482436588709364</v>
+        <v>-8.93692477138816</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.455713651194375</v>
       </c>
       <c r="E12">
-        <v>-11.64386351130005</v>
+        <v>-13.0354364030131</v>
       </c>
       <c r="F12">
-        <v>-3.70864951548036</v>
+        <v>-3.297544799126926</v>
       </c>
       <c r="G12">
-        <v>-6.553017481286674</v>
+        <v>-7.475626796535083</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.103869246503428</v>
       </c>
       <c r="E13">
-        <v>-13.82445960021355</v>
+        <v>-14.28070788496035</v>
       </c>
       <c r="F13">
-        <v>-3.458044683274179</v>
+        <v>-3.377161654760855</v>
       </c>
       <c r="G13">
-        <v>-7.099283979630735</v>
+        <v>-7.643226475006227</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>2.683605060708197</v>
       </c>
       <c r="E14">
-        <v>-15.08968806711261</v>
+        <v>-15.50389399917219</v>
       </c>
       <c r="F14">
-        <v>-3.222842182948605</v>
+        <v>-3.308390017235855</v>
       </c>
       <c r="G14">
-        <v>-7.134269824889753</v>
+        <v>-7.511602494910343</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>3.136481381885522</v>
       </c>
       <c r="E15">
-        <v>-15.39753825862804</v>
+        <v>-15.43468080243896</v>
       </c>
       <c r="F15">
-        <v>-3.202744954881678</v>
+        <v>-2.978630771523053</v>
       </c>
       <c r="G15">
-        <v>-6.329873469757639</v>
+        <v>-6.630288924718803</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.415815916208193</v>
       </c>
       <c r="E16">
-        <v>-16.44490184101808</v>
+        <v>-16.383459505682</v>
       </c>
       <c r="F16">
-        <v>-2.646277415520762</v>
+        <v>-2.581773073584913</v>
       </c>
       <c r="G16">
-        <v>-6.226286499833844</v>
+        <v>-6.4251708336511</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.494964402045913</v>
       </c>
       <c r="E17">
-        <v>-17.43742107470121</v>
+        <v>-17.60085823011204</v>
       </c>
       <c r="F17">
-        <v>-2.756817712859562</v>
+        <v>-2.551734923486773</v>
       </c>
       <c r="G17">
-        <v>-6.167199883048932</v>
+        <v>-5.389069396225397</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>3.370006666152815</v>
       </c>
       <c r="E18">
-        <v>-18.00470754211608</v>
+        <v>-17.77888160030158</v>
       </c>
       <c r="F18">
-        <v>-2.372261450619598</v>
+        <v>-2.341429072004865</v>
       </c>
       <c r="G18">
-        <v>-5.632113096990991</v>
+        <v>-4.971794994273499</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.057351364762908</v>
       </c>
       <c r="E19">
-        <v>-19.2288219934995</v>
+        <v>-19.34579247711762</v>
       </c>
       <c r="F19">
-        <v>-1.947527361157892</v>
+        <v>-2.132468578698123</v>
       </c>
       <c r="G19">
-        <v>-4.81375948186531</v>
+        <v>-4.788940321957394</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.589575239424928</v>
       </c>
       <c r="E20">
-        <v>-20.45031445843247</v>
+        <v>-20.61848386918131</v>
       </c>
       <c r="F20">
-        <v>-1.745816281679074</v>
+        <v>-1.56323082668806</v>
       </c>
       <c r="G20">
-        <v>-4.559469857902812</v>
+        <v>-5.613550868152297</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.009159514327611</v>
       </c>
       <c r="E21">
-        <v>-20.20130272969869</v>
+        <v>-19.95388502381561</v>
       </c>
       <c r="F21">
-        <v>-1.259126033099462</v>
+        <v>-1.501042654653542</v>
       </c>
       <c r="G21">
-        <v>-5.373887234382299</v>
+        <v>-4.915668005200695</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.36221743934278</v>
       </c>
       <c r="E22">
-        <v>-20.74784425768443</v>
+        <v>-21.10578390019871</v>
       </c>
       <c r="F22">
-        <v>-1.094826046608112</v>
+        <v>-1.02112749998018</v>
       </c>
       <c r="G22">
-        <v>-4.930125157570693</v>
+        <v>-5.20790310213432</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.6935455074479212</v>
       </c>
       <c r="E23">
-        <v>-21.57303637678414</v>
+        <v>-21.35123624836245</v>
       </c>
       <c r="F23">
-        <v>-1.000232084131871</v>
+        <v>-0.9654372733167091</v>
       </c>
       <c r="G23">
-        <v>-5.582540988085944</v>
+        <v>-5.692318678168176</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.0436782161866841</v>
       </c>
       <c r="E24">
-        <v>-21.61519646979555</v>
+        <v>-20.85884168408644</v>
       </c>
       <c r="F24">
-        <v>-0.8977900669916709</v>
+        <v>-1.146199090946095</v>
       </c>
       <c r="G24">
-        <v>-5.257839371048687</v>
+        <v>-4.379922420580439</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.5530921875766401</v>
       </c>
       <c r="E25">
-        <v>-22.12561888909611</v>
+        <v>-22.8826665313284</v>
       </c>
       <c r="F25">
-        <v>-0.732904901164566</v>
+        <v>-0.916815126153845</v>
       </c>
       <c r="G25">
-        <v>-5.581339260055189</v>
+        <v>-5.255846422634045</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.069969614502438</v>
       </c>
       <c r="E26">
-        <v>-21.74884985165794</v>
+        <v>-22.09890089245085</v>
       </c>
       <c r="F26">
-        <v>-0.7580763229845605</v>
+        <v>-0.7623174874261074</v>
       </c>
       <c r="G26">
-        <v>-5.850619034219507</v>
+        <v>-5.579250305819908</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.487693970977825</v>
       </c>
       <c r="E27">
-        <v>-22.66193512277253</v>
+        <v>-23.25011596925879</v>
       </c>
       <c r="F27">
-        <v>-0.8411100241310507</v>
+        <v>-0.5966594731122681</v>
       </c>
       <c r="G27">
-        <v>-6.235989708809448</v>
+        <v>-5.932048522848961</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.795064193496471</v>
       </c>
       <c r="E28">
-        <v>-22.91707387683868</v>
+        <v>-21.34342463069923</v>
       </c>
       <c r="F28">
-        <v>-1.029002477644702</v>
+        <v>-0.9290072861438555</v>
       </c>
       <c r="G28">
-        <v>-6.317525134896158</v>
+        <v>-6.504107481489482</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.987446764884863</v>
       </c>
       <c r="E29">
-        <v>-23.08936419893451</v>
+        <v>-21.50707915286242</v>
       </c>
       <c r="F29">
-        <v>-1.069470123048969</v>
+        <v>-0.847709326680687</v>
       </c>
       <c r="G29">
-        <v>-6.336186680101029</v>
+        <v>-6.632516921866733</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.065575050450068</v>
       </c>
       <c r="E30">
-        <v>-22.13629250233219</v>
+        <v>-22.23646234738186</v>
       </c>
       <c r="F30">
-        <v>-0.8905192731338883</v>
+        <v>-0.7750964104577883</v>
       </c>
       <c r="G30">
-        <v>-6.240002090003045</v>
+        <v>-6.129969487914289</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.032290261343471</v>
       </c>
       <c r="E31">
-        <v>-22.25958473566502</v>
+        <v>-21.51767125356636</v>
       </c>
       <c r="F31">
-        <v>-0.8917387266887767</v>
+        <v>-0.9069644753598116</v>
       </c>
       <c r="G31">
-        <v>-6.010346235398263</v>
+        <v>-6.385311865358275</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.894739668701194</v>
       </c>
       <c r="E32">
-        <v>-21.35931957446615</v>
+        <v>-20.66950165735173</v>
       </c>
       <c r="F32">
-        <v>-0.9311650854536418</v>
+        <v>-1.041778233264552</v>
       </c>
       <c r="G32">
-        <v>-6.391674733884754</v>
+        <v>-6.890706368474492</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.665078150409038</v>
       </c>
       <c r="E33">
-        <v>-20.78381845520136</v>
+        <v>-21.67036234015699</v>
       </c>
       <c r="F33">
-        <v>-1.072496585053373</v>
+        <v>-0.9399023909891212</v>
       </c>
       <c r="G33">
-        <v>-6.140414259090689</v>
+        <v>-6.247785182565871</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.360916290043557</v>
       </c>
       <c r="E34">
-        <v>-21.23961389254739</v>
+        <v>-20.09142836485059</v>
       </c>
       <c r="F34">
-        <v>-1.08562075597462</v>
+        <v>-1.0634726287472</v>
       </c>
       <c r="G34">
-        <v>-5.913214829276046</v>
+        <v>-6.691742581564294</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.005351201319367</v>
       </c>
       <c r="E35">
-        <v>-20.49587996389765</v>
+        <v>-21.52735313099476</v>
       </c>
       <c r="F35">
-        <v>-0.9686989156495567</v>
+        <v>-0.9529370825261456</v>
       </c>
       <c r="G35">
-        <v>-5.425088131692667</v>
+        <v>-5.909232242992303</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.6250117387617053</v>
       </c>
       <c r="E36">
-        <v>-19.77886856036717</v>
+        <v>-20.071598177171</v>
       </c>
       <c r="F36">
-        <v>-1.024439029049363</v>
+        <v>-0.6430921468470372</v>
       </c>
       <c r="G36">
-        <v>-5.052433262519067</v>
+        <v>-6.353477659452643</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.2475913160437135</v>
       </c>
       <c r="E37">
-        <v>-19.17942539902383</v>
+        <v>-19.43348184780215</v>
       </c>
       <c r="F37">
-        <v>-1.288936921398737</v>
+        <v>-0.9078854003496396</v>
       </c>
       <c r="G37">
-        <v>-5.096529729102159</v>
+        <v>-4.978382979896649</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.1011912050527738</v>
       </c>
       <c r="E38">
-        <v>-18.80798184701867</v>
+        <v>-18.67122646046104</v>
       </c>
       <c r="F38">
-        <v>-0.9404899458837492</v>
+        <v>-1.175709075121435</v>
       </c>
       <c r="G38">
-        <v>-4.674239850658266</v>
+        <v>-5.821390227653281</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.4009506928002737</v>
       </c>
       <c r="E39">
-        <v>-18.42459218058129</v>
+        <v>-17.96794991859582</v>
       </c>
       <c r="F39">
-        <v>-1.411844378231203</v>
+        <v>-0.4730757738539085</v>
       </c>
       <c r="G39">
-        <v>-4.5653361445984</v>
+        <v>-5.456518451042507</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.641443418124526</v>
       </c>
       <c r="E40">
-        <v>-17.6821896232898</v>
+        <v>-17.92191345183385</v>
       </c>
       <c r="F40">
-        <v>-1.320298257789226</v>
+        <v>-1.012040195437388</v>
       </c>
       <c r="G40">
-        <v>-4.674203434657334</v>
+        <v>-4.434867544895723</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.821918445311508</v>
       </c>
       <c r="E41">
-        <v>-17.71800532421647</v>
+        <v>-17.32090796695786</v>
       </c>
       <c r="F41">
-        <v>-1.394616033430095</v>
+        <v>-0.7837695759036925</v>
       </c>
       <c r="G41">
-        <v>-5.112585874967624</v>
+        <v>-4.329582265110282</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.9501826243273963</v>
       </c>
       <c r="E42">
-        <v>-18.03085042256237</v>
+        <v>-18.42174829890447</v>
       </c>
       <c r="F42">
-        <v>-1.278488421621625</v>
+        <v>-0.7644238162936419</v>
       </c>
       <c r="G42">
-        <v>-4.832272052520914</v>
+        <v>-5.004844170392043</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.039207271503655</v>
       </c>
       <c r="E43">
-        <v>-16.5539610805448</v>
+        <v>-16.80621519666807</v>
       </c>
       <c r="F43">
-        <v>-1.444694398182206</v>
+        <v>-1.461273423557984</v>
       </c>
       <c r="G43">
-        <v>-4.5516205544292</v>
+        <v>-5.84892072435786</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.102684077740692</v>
       </c>
       <c r="E44">
-        <v>-16.66496756389482</v>
+        <v>-16.2357406835518</v>
       </c>
       <c r="F44">
-        <v>-1.22404298780769</v>
+        <v>-1.229608922247502</v>
       </c>
       <c r="G44">
-        <v>-3.812958391524856</v>
+        <v>-5.615755691481452</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.152468101875601</v>
       </c>
       <c r="E45">
-        <v>-15.64398234259947</v>
+        <v>-15.65701529079355</v>
       </c>
       <c r="F45">
-        <v>-1.372022884840436</v>
+        <v>-1.014889282379264</v>
       </c>
       <c r="G45">
-        <v>-4.466834172622925</v>
+        <v>-5.410230403312418</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.196879818936588</v>
       </c>
       <c r="E46">
-        <v>-15.85938826572233</v>
+        <v>-15.49027234935712</v>
       </c>
       <c r="F46">
-        <v>-1.636907201433176</v>
+        <v>-1.232024865621504</v>
       </c>
       <c r="G46">
-        <v>-5.208565211242174</v>
+        <v>-5.067337338536865</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.239164493046524</v>
       </c>
       <c r="E47">
-        <v>-15.5159442685066</v>
+        <v>-16.24978800992359</v>
       </c>
       <c r="F47">
-        <v>-1.679120090756257</v>
+        <v>-1.480589092755641</v>
       </c>
       <c r="G47">
-        <v>-5.254237497501959</v>
+        <v>-4.97824062643846</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.277820373850834</v>
       </c>
       <c r="E48">
-        <v>-14.65951926417598</v>
+        <v>-15.5594538467723</v>
       </c>
       <c r="F48">
-        <v>-1.472261967052261</v>
+        <v>-1.501058491712696</v>
       </c>
       <c r="G48">
-        <v>-4.751322592994656</v>
+        <v>-6.250863989917393</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.307693202805667</v>
       </c>
       <c r="E49">
-        <v>-14.13770773274614</v>
+        <v>-14.94408857081799</v>
       </c>
       <c r="F49">
-        <v>-1.808051964891056</v>
+        <v>-1.586420240554882</v>
       </c>
       <c r="G49">
-        <v>-4.617752012121681</v>
+        <v>-5.379640962529552</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.320744826271085</v>
       </c>
       <c r="E50">
-        <v>-14.16739640834042</v>
+        <v>-13.87447206715427</v>
       </c>
       <c r="F50">
-        <v>-2.013057944526946</v>
+        <v>-1.99310641740424</v>
       </c>
       <c r="G50">
-        <v>-5.188228529994431</v>
+        <v>-5.89316947603576</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.308290513649176</v>
       </c>
       <c r="E51">
-        <v>-13.03131096319211</v>
+        <v>-14.60300390856026</v>
       </c>
       <c r="F51">
-        <v>-1.87273843300718</v>
+        <v>-1.947852020870558</v>
       </c>
       <c r="G51">
-        <v>-4.460967885927337</v>
+        <v>-5.191853577359933</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.263004955516571</v>
       </c>
       <c r="E52">
-        <v>-13.24197104555493</v>
+        <v>-14.28421745231629</v>
       </c>
       <c r="F52">
-        <v>-2.110780518039137</v>
+        <v>-1.476306751960293</v>
       </c>
       <c r="G52">
-        <v>-4.758771320458016</v>
+        <v>-5.731174551162602</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.17918651300705</v>
       </c>
       <c r="E53">
-        <v>-13.0334891591898</v>
+        <v>-12.5718655757959</v>
       </c>
       <c r="F53">
-        <v>-2.099213130032767</v>
+        <v>-1.298453410244612</v>
       </c>
       <c r="G53">
-        <v>-4.939546970175458</v>
+        <v>-4.345323909149516</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.054240167290834</v>
       </c>
       <c r="E54">
-        <v>-11.93724069988697</v>
+        <v>-12.49515775457997</v>
       </c>
       <c r="F54">
-        <v>-2.438428683766658</v>
+        <v>-1.580234285249176</v>
       </c>
       <c r="G54">
-        <v>-5.11960092096534</v>
+        <v>-5.400921149255987</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.888582477652899</v>
       </c>
       <c r="E55">
-        <v>-12.50601250677636</v>
+        <v>-12.24900349294504</v>
       </c>
       <c r="F55">
-        <v>-1.989704617097876</v>
+        <v>-2.000149157610199</v>
       </c>
       <c r="G55">
-        <v>-5.459858791491632</v>
+        <v>-5.825690626308795</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.6856516059219935</v>
       </c>
       <c r="E56">
-        <v>-11.7291437338125</v>
+        <v>-12.70509328110156</v>
       </c>
       <c r="F56">
-        <v>-2.297717996885778</v>
+        <v>-1.412100938589505</v>
       </c>
       <c r="G56">
-        <v>-5.484605119397685</v>
+        <v>-5.64933455488628</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.4496386377602011</v>
       </c>
       <c r="E57">
-        <v>-11.52191170627348</v>
+        <v>-12.38980280679152</v>
       </c>
       <c r="F57">
-        <v>-2.134595495742558</v>
+        <v>-2.337053292560506</v>
       </c>
       <c r="G57">
-        <v>-5.706050821065073</v>
+        <v>-5.849185568001002</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.1873637377782254</v>
       </c>
       <c r="E58">
-        <v>-11.55180416319812</v>
+        <v>-11.21427888151041</v>
       </c>
       <c r="F58">
-        <v>-2.535120264727898</v>
+        <v>-2.473634466266877</v>
       </c>
       <c r="G58">
-        <v>-5.971490362403837</v>
+        <v>-6.689481478960972</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.09316952522304683</v>
       </c>
       <c r="E59">
-        <v>-11.25313771697023</v>
+        <v>-11.60117811530375</v>
       </c>
       <c r="F59">
-        <v>-2.395459574868955</v>
+        <v>-2.150960720819751</v>
       </c>
       <c r="G59">
-        <v>-5.203569598023414</v>
+        <v>-5.850483301852397</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.3827715855672145</v>
       </c>
       <c r="E60">
-        <v>-11.01783367905767</v>
+        <v>-11.31380568325099</v>
       </c>
       <c r="F60">
-        <v>-2.643989752325909</v>
+        <v>-1.864585514954498</v>
       </c>
       <c r="G60">
-        <v>-5.859756139907895</v>
+        <v>-6.098158455827432</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.6724038611388701</v>
       </c>
       <c r="E61">
-        <v>-10.35659043293166</v>
+        <v>-10.90105791982188</v>
       </c>
       <c r="F61">
-        <v>-2.494394475259415</v>
+        <v>-1.790549638966577</v>
       </c>
       <c r="G61">
-        <v>-5.464890820711324</v>
+        <v>-5.844739505341761</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.9528187919718087</v>
       </c>
       <c r="E62">
-        <v>-10.38085852513876</v>
+        <v>-10.67937553172439</v>
       </c>
       <c r="F62">
-        <v>-2.468172264564526</v>
+        <v>-2.146725099348909</v>
       </c>
       <c r="G62">
-        <v>-6.195087918671752</v>
+        <v>-6.80423160844319</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.21456890833989</v>
       </c>
       <c r="E63">
-        <v>-10.73158883703283</v>
+        <v>-10.57473608282915</v>
       </c>
       <c r="F63">
-        <v>-2.270715019174578</v>
+        <v>-2.062683369387241</v>
       </c>
       <c r="G63">
-        <v>-5.213948158289029</v>
+        <v>-6.238578555421158</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.448152304011731</v>
       </c>
       <c r="E64">
-        <v>-9.919298340380967</v>
+        <v>-9.758397130414432</v>
       </c>
       <c r="F64">
-        <v>-2.427573171569278</v>
+        <v>-1.783940834181448</v>
       </c>
       <c r="G64">
-        <v>-6.353937825282602</v>
+        <v>-7.250244856221501</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.644790546096549</v>
       </c>
       <c r="E65">
-        <v>-9.584630525792106</v>
+        <v>-10.35284085645331</v>
       </c>
       <c r="F65">
-        <v>-2.400342140206255</v>
+        <v>-2.063557575052564</v>
       </c>
       <c r="G65">
-        <v>-6.046186201406413</v>
+        <v>-7.238773815927926</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.796831551610823</v>
       </c>
       <c r="E66">
-        <v>-10.84207907434598</v>
+        <v>-9.581514935674829</v>
       </c>
       <c r="F66">
-        <v>-2.480822907417056</v>
+        <v>-2.505440032166647</v>
       </c>
       <c r="G66">
-        <v>-6.337937958691304</v>
+        <v>-6.622840197255443</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.898601345234246</v>
       </c>
       <c r="E67">
-        <v>-10.37841767764863</v>
+        <v>-8.925234897061216</v>
       </c>
       <c r="F67">
-        <v>-2.552754830096316</v>
+        <v>-2.288190422098495</v>
       </c>
       <c r="G67">
-        <v>-6.01108779759906</v>
+        <v>-6.933021761557457</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.948145526909544</v>
       </c>
       <c r="E68">
-        <v>-9.791500275410502</v>
+        <v>-9.771104028479956</v>
       </c>
       <c r="F68">
-        <v>-2.728446413237422</v>
+        <v>-2.038116131373986</v>
       </c>
       <c r="G68">
-        <v>-6.44660992656342</v>
+        <v>-6.781921842054041</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.947894250735119</v>
       </c>
       <c r="E69">
-        <v>-9.574500329436948</v>
+        <v>-9.760982889072812</v>
       </c>
       <c r="F69">
-        <v>-2.649499465205723</v>
+        <v>-2.460480204933237</v>
       </c>
       <c r="G69">
-        <v>-6.978336508899001</v>
+        <v>-6.830295533473872</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.903937723150924</v>
       </c>
       <c r="E70">
-        <v>-8.886996462540449</v>
+        <v>-8.629865179910917</v>
       </c>
       <c r="F70">
-        <v>-2.514780729655909</v>
+        <v>-2.260785183084773</v>
       </c>
       <c r="G70">
-        <v>-6.850781189270882</v>
+        <v>-7.193210777670937</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.823439186590064</v>
       </c>
       <c r="E71">
-        <v>-10.52182992099754</v>
+        <v>-9.941542204706645</v>
       </c>
       <c r="F71">
-        <v>-2.602455480987595</v>
+        <v>-2.096785308864399</v>
       </c>
       <c r="G71">
-        <v>-7.204479874686616</v>
+        <v>-7.28667740988118</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.71511555713805</v>
       </c>
       <c r="E72">
-        <v>-10.38142458438972</v>
+        <v>-10.12138602144726</v>
       </c>
       <c r="F72">
-        <v>-2.624085736380667</v>
+        <v>-2.673499736501251</v>
       </c>
       <c r="G72">
-        <v>-6.616331664725236</v>
+        <v>-7.50498471437734</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.590622358071135</v>
       </c>
       <c r="E73">
-        <v>-9.371176374966556</v>
+        <v>-10.43339335210175</v>
       </c>
       <c r="F73">
-        <v>-2.792721117815532</v>
+        <v>-2.024338681762621</v>
       </c>
       <c r="G73">
-        <v>-6.200798609726995</v>
+        <v>-7.781769495279186</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.463143425804775</v>
       </c>
       <c r="E74">
-        <v>-9.590884348396697</v>
+        <v>-10.85249003608961</v>
       </c>
       <c r="F74">
-        <v>-2.507668306389671</v>
+        <v>-2.748320338770272</v>
       </c>
       <c r="G74">
-        <v>-6.629785721796834</v>
+        <v>-6.832020327699833</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.343607040378745</v>
       </c>
       <c r="E75">
-        <v>-10.87557166810671</v>
+        <v>-10.79888648926082</v>
       </c>
       <c r="F75">
-        <v>-2.854831688260194</v>
+        <v>-2.492942216934957</v>
       </c>
       <c r="G75">
-        <v>-6.316055252676722</v>
+        <v>-6.547137952408929</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.239161479958315</v>
       </c>
       <c r="E76">
-        <v>-11.37633485234891</v>
+        <v>-11.56796628693149</v>
       </c>
       <c r="F76">
-        <v>-3.253901823362203</v>
+        <v>-2.932351717262082</v>
       </c>
       <c r="G76">
-        <v>-6.725798163526777</v>
+        <v>-7.772509899405844</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.154375778028861</v>
       </c>
       <c r="E77">
-        <v>-11.11075796569507</v>
+        <v>-11.48288984574939</v>
       </c>
       <c r="F77">
-        <v>-3.096857585522439</v>
+        <v>-2.549208912551647</v>
       </c>
       <c r="G77">
-        <v>-6.668744221702977</v>
+        <v>-6.940288409016158</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.091981871683878</v>
       </c>
       <c r="E78">
-        <v>-11.98946306214343</v>
+        <v>-10.80805664912635</v>
       </c>
       <c r="F78">
-        <v>-3.169931360166731</v>
+        <v>-2.517271899060896</v>
       </c>
       <c r="G78">
-        <v>-6.787126019641776</v>
+        <v>-7.358145466982966</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.052880869470328</v>
       </c>
       <c r="E79">
-        <v>-11.72805690005065</v>
+        <v>-11.19008324488743</v>
       </c>
       <c r="F79">
-        <v>-3.184448400440606</v>
+        <v>-2.452107943611266</v>
       </c>
       <c r="G79">
-        <v>-6.843845596366109</v>
+        <v>-6.899694499613614</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.036854320199279</v>
       </c>
       <c r="E80">
-        <v>-12.49898884359046</v>
+        <v>-12.08128692959696</v>
       </c>
       <c r="F80">
-        <v>-2.939822849918167</v>
+        <v>-2.804547441739076</v>
       </c>
       <c r="G80">
-        <v>-6.809058383839448</v>
+        <v>-6.757360904698189</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.043670722352874</v>
       </c>
       <c r="E81">
-        <v>-12.80104258837608</v>
+        <v>-12.9397950319711</v>
       </c>
       <c r="F81">
-        <v>-3.405984310568896</v>
+        <v>-3.045338048387278</v>
       </c>
       <c r="G81">
-        <v>-6.737103676543388</v>
+        <v>-7.218930405965534</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.074550127689719</v>
       </c>
       <c r="E82">
-        <v>-13.9902108058423</v>
+        <v>-13.53269001989935</v>
       </c>
       <c r="F82">
-        <v>-3.250776379738084</v>
+        <v>-3.028626783567562</v>
       </c>
       <c r="G82">
-        <v>-6.237982657224089</v>
+        <v>-6.989049434264083</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.132081670844626</v>
       </c>
       <c r="E83">
-        <v>-14.27267890054475</v>
+        <v>-14.94059258888407</v>
       </c>
       <c r="F83">
-        <v>-3.186234820713222</v>
+        <v>-3.101776576095794</v>
       </c>
       <c r="G83">
-        <v>-6.783457935184264</v>
+        <v>-6.838853293692888</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.220914221561574</v>
       </c>
       <c r="E84">
-        <v>-16.16197184196685</v>
+        <v>-15.04152321756702</v>
       </c>
       <c r="F84">
-        <v>-3.135379648209588</v>
+        <v>-2.918921099246198</v>
       </c>
       <c r="G84">
-        <v>-7.005615404142596</v>
+        <v>-7.268747495240487</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.347531120935699</v>
       </c>
       <c r="E85">
-        <v>-17.32369297847258</v>
+        <v>-16.72904999957737</v>
       </c>
       <c r="F85">
-        <v>-3.139230429142979</v>
+        <v>-3.143654511617759</v>
       </c>
       <c r="G85">
-        <v>-6.816669328034232</v>
+        <v>-6.754983933000992</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.520598897858573</v>
       </c>
       <c r="E86">
-        <v>-16.57118739566998</v>
+        <v>-18.07980775505929</v>
       </c>
       <c r="F86">
-        <v>-3.262621708132613</v>
+        <v>-3.010677852574928</v>
       </c>
       <c r="G86">
-        <v>-7.100071889469081</v>
+        <v>-7.130611672068857</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.74814896125035</v>
       </c>
       <c r="E87">
-        <v>-18.44357554362144</v>
+        <v>-17.71607166581519</v>
       </c>
       <c r="F87">
-        <v>-3.746479498682461</v>
+        <v>-3.265523057369698</v>
       </c>
       <c r="G87">
-        <v>-6.809492065305092</v>
+        <v>-7.059848761166936</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.034730479584511</v>
       </c>
       <c r="E88">
-        <v>-20.86952888274454</v>
+        <v>-19.58597821001045</v>
       </c>
       <c r="F88">
-        <v>-3.354159118192055</v>
+        <v>-3.067309592405127</v>
       </c>
       <c r="G88">
-        <v>-6.462785252068299</v>
+        <v>-7.095831080633275</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.382232562262788</v>
       </c>
       <c r="E89">
-        <v>-21.80548294759786</v>
+        <v>-21.2554997793663</v>
       </c>
       <c r="F89">
-        <v>-3.414994013521831</v>
+        <v>-3.55756951411814</v>
       </c>
       <c r="G89">
-        <v>-6.484919559543866</v>
+        <v>-7.296420345403256</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.789841952197502</v>
       </c>
       <c r="E90">
-        <v>-23.38047262204359</v>
+        <v>-21.83120467996143</v>
       </c>
       <c r="F90">
-        <v>-3.449225816884054</v>
+        <v>-3.167749805268213</v>
       </c>
       <c r="G90">
-        <v>-6.694924015827534</v>
+        <v>-7.178015373645682</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.255782481935675</v>
       </c>
       <c r="E91">
-        <v>-25.00382187041723</v>
+        <v>-23.80458685523196</v>
       </c>
       <c r="F91">
-        <v>-3.119110237340279</v>
+        <v>-3.204113276792618</v>
       </c>
       <c r="G91">
-        <v>-7.050496470018495</v>
+        <v>-6.698774180289706</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.771982872803025</v>
       </c>
       <c r="E92">
-        <v>-27.10683614263133</v>
+        <v>-25.50289140538056</v>
       </c>
       <c r="F92">
-        <v>-3.312095097225026</v>
+        <v>-2.71362609328074</v>
       </c>
       <c r="G92">
-        <v>-7.119435270328278</v>
+        <v>-6.896635555535328</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.32460259167344</v>
       </c>
       <c r="E93">
-        <v>-29.10110816849924</v>
+        <v>-28.69967706161529</v>
       </c>
       <c r="F93">
-        <v>-3.277674041005907</v>
+        <v>-2.810311339418318</v>
       </c>
       <c r="G93">
-        <v>-8.043355561610237</v>
+        <v>-6.91901815392634</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.893843976503593</v>
       </c>
       <c r="E94">
-        <v>-31.18518209817625</v>
+        <v>-29.55506278116115</v>
       </c>
       <c r="F94">
-        <v>-3.065773397667151</v>
+        <v>-3.102954853296881</v>
       </c>
       <c r="G94">
-        <v>-7.202016828805398</v>
+        <v>-6.978859575094206</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.460218978879753</v>
       </c>
       <c r="E95">
-        <v>-33.60096901315213</v>
+        <v>-32.33103546175911</v>
       </c>
       <c r="F95">
-        <v>-2.952093403350992</v>
+        <v>-3.233908328032738</v>
       </c>
       <c r="G95">
-        <v>-8.106557186500465</v>
+        <v>-7.213362068368481</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.998452886922602</v>
       </c>
       <c r="E96">
-        <v>-35.67294286028065</v>
+        <v>-34.63197801166346</v>
       </c>
       <c r="F96">
-        <v>-2.867868755356092</v>
+        <v>-2.944497949780545</v>
       </c>
       <c r="G96">
-        <v>-7.546171211431413</v>
+        <v>-7.726006666215702</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.483047682439364</v>
       </c>
       <c r="E97">
-        <v>-37.88392953825964</v>
+        <v>-37.16418520066553</v>
       </c>
       <c r="F97">
-        <v>-2.918653452946488</v>
+        <v>-2.650950931677224</v>
       </c>
       <c r="G97">
-        <v>-7.817556492558707</v>
+        <v>-8.093182582521809</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.891987899067736</v>
       </c>
       <c r="E98">
-        <v>-41.81382758735912</v>
+        <v>-39.24502353566406</v>
       </c>
       <c r="F98">
-        <v>-2.508194888606554</v>
+        <v>-2.824746026984591</v>
       </c>
       <c r="G98">
-        <v>-8.540675644156174</v>
+        <v>-7.941019977900288</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.216317568214844</v>
       </c>
       <c r="E99">
-        <v>-42.8307552959436</v>
+        <v>-41.77131653761212</v>
       </c>
       <c r="F99">
-        <v>-2.622046715014538</v>
+        <v>-2.829918410504416</v>
       </c>
       <c r="G99">
-        <v>-8.516670878450919</v>
+        <v>-9.001175839214335</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.454580258197883</v>
       </c>
       <c r="E100">
-        <v>-45.80598309711606</v>
+        <v>-44.96149062179565</v>
       </c>
       <c r="F100">
-        <v>-2.467092968983154</v>
+        <v>-2.655190512412855</v>
       </c>
       <c r="G100">
-        <v>-9.116409308345286</v>
+        <v>-8.311513060836743</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.615174314797898</v>
       </c>
       <c r="E101">
-        <v>-48.24541770335999</v>
+        <v>-47.36775868440741</v>
       </c>
       <c r="F101">
-        <v>-2.741463684009377</v>
+        <v>-2.494879881122497</v>
       </c>
       <c r="G101">
-        <v>-9.731578190998198</v>
+        <v>-8.818678705816472</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.710665690939233</v>
       </c>
       <c r="E102">
-        <v>-50.52533568056523</v>
+        <v>-50.30991277566484</v>
       </c>
       <c r="F102">
-        <v>-2.115397812635601</v>
+        <v>-2.411009191399697</v>
       </c>
       <c r="G102">
-        <v>-9.574029328784283</v>
+        <v>-8.990045785111306</v>
       </c>
     </row>
   </sheetData>
